--- a/assets/class-materials/finc-612-ftmba-fall-2026-module-04-class-examples.xlsx
+++ b/assets/class-materials/finc-612-ftmba-fall-2026-module-04-class-examples.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/boone_bowles_tamu_edu/Documents/tbowles/02teaching/00finc612/2026_fall/classes/2026-10-29/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/boone_bowles_tamu_edu/Documents/tbowles/02teaching/00finc612/2026_fall/classes/2026-10-30/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{84B9A446-E3E3-417A-A4C9-9BB304104F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4C4D234-D721-48DC-8472-DF701AA62BAC}"/>
+  <xr:revisionPtr revIDLastSave="973" documentId="8_{84B9A446-E3E3-417A-A4C9-9BB304104F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4849804B-2C9C-440F-9387-A658605F853B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB0CD863-C184-42D3-8F31-2AA00282EC54}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{EB0CD863-C184-42D3-8F31-2AA00282EC54}"/>
   </bookViews>
   <sheets>
     <sheet name="MBA" sheetId="1" r:id="rId1"/>
     <sheet name="Web Hosting" sheetId="2" r:id="rId2"/>
     <sheet name="Maroon" sheetId="3" r:id="rId3"/>
     <sheet name="Graphite" sheetId="4" r:id="rId4"/>
+    <sheet name="Homenet" sheetId="5" r:id="rId5"/>
+    <sheet name="Homenet_cannibal" sheetId="6" r:id="rId6"/>
+    <sheet name="Homenet_nwc" sheetId="7" r:id="rId7"/>
+    <sheet name="Homenet_rent" sheetId="8" r:id="rId8"/>
+    <sheet name="Homenet_cashbuffer" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="100">
   <si>
     <t>Run the business</t>
   </si>
@@ -154,12 +159,239 @@
   <si>
     <t>Project Maroon</t>
   </si>
+  <si>
+    <t>Homenet Assumptions:</t>
+  </si>
+  <si>
+    <t>Research and Development_0</t>
+  </si>
+  <si>
+    <t>Sales Forecast (units/year)_2-5</t>
+  </si>
+  <si>
+    <t>Retail Price (per unit)</t>
+  </si>
+  <si>
+    <t>Wholesale Price (per unit)</t>
+  </si>
+  <si>
+    <t>Production and Packaging (per unit) cogs</t>
+  </si>
+  <si>
+    <t>Engineers</t>
+  </si>
+  <si>
+    <t>Software Development (1 year):</t>
+  </si>
+  <si>
+    <t>Cost per engineer per year</t>
+  </si>
+  <si>
+    <t>Total Software Development Cost</t>
+  </si>
+  <si>
+    <t>New Equipment + Install</t>
+  </si>
+  <si>
+    <t>Annual Depreciation (SL for 5 years)_2-6</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Marketing and Support Costs (per year)_2-5</t>
+  </si>
+  <si>
+    <t>NOPAT:</t>
+  </si>
+  <si>
+    <t>Sales in units</t>
+  </si>
+  <si>
+    <t>Revenue (in $s)</t>
+  </si>
+  <si>
+    <t>Less: COGS</t>
+  </si>
+  <si>
+    <t>Gross Profit</t>
+  </si>
+  <si>
+    <t>Expenses:</t>
+  </si>
+  <si>
+    <t>Engineering and Design</t>
+  </si>
+  <si>
+    <t>Software Engineers</t>
+  </si>
+  <si>
+    <t>Marketing and Support</t>
+  </si>
+  <si>
+    <t>Total Engineering and Design_1</t>
+  </si>
+  <si>
+    <t>Depreciation Expense</t>
+  </si>
+  <si>
+    <t>Total Expenses</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>NOPAT = (EBIT x (1-t))</t>
+  </si>
+  <si>
+    <t>CAPEX &amp; DEPRECIATION:</t>
+  </si>
+  <si>
+    <t>Purchase of equipment</t>
+  </si>
+  <si>
+    <t>Capex &amp; Depreciation</t>
+  </si>
+  <si>
+    <t>Increases in NWC:</t>
+  </si>
+  <si>
+    <t>Increases in NWC</t>
+  </si>
+  <si>
+    <t>Free Cash Flow</t>
+  </si>
+  <si>
+    <t>PV(FCF)</t>
+  </si>
+  <si>
+    <t>Cannibalization:</t>
+  </si>
+  <si>
+    <t>Cannibalization Rate</t>
+  </si>
+  <si>
+    <t>Sales price of old product (per unit)</t>
+  </si>
+  <si>
+    <t>COGS per unit of old product</t>
+  </si>
+  <si>
+    <t>New Revenue (in $s homenet)</t>
+  </si>
+  <si>
+    <t>Lost Sales in units (old product)</t>
+  </si>
+  <si>
+    <t>Lost Revenue (in $s old product)</t>
+  </si>
+  <si>
+    <t>Incremental Revenue</t>
+  </si>
+  <si>
+    <t>New COGS (homenet)</t>
+  </si>
+  <si>
+    <t>Saved COGS (old product)</t>
+  </si>
+  <si>
+    <t>Incremental COGS</t>
+  </si>
+  <si>
+    <t>Incremental Gross Profit</t>
+  </si>
+  <si>
+    <t>Incremental EBIT</t>
+  </si>
+  <si>
+    <t>Incremental NOPAT = (EBIT x (1-t))</t>
+  </si>
+  <si>
+    <r>
+      <t>New Sales in units (homenet)</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Here is my note.</t>
+    </r>
+  </si>
+  <si>
+    <t>NWC:</t>
+  </si>
+  <si>
+    <t>ARs maintain as a percentage of sales</t>
+  </si>
+  <si>
+    <t>APs maintain as a percentage of COGS</t>
+  </si>
+  <si>
+    <t>Level of ARs</t>
+  </si>
+  <si>
+    <t>Level of APs</t>
+  </si>
+  <si>
+    <t>Level of NWC</t>
+  </si>
+  <si>
+    <t>Changes in NWC</t>
+  </si>
+  <si>
+    <t>Annual Rent of building (foregone)</t>
+  </si>
+  <si>
+    <t>Lost Rent Revenue</t>
+  </si>
+  <si>
+    <t>Cash Infusion at Year 0 (maintain until end)</t>
+  </si>
+  <si>
+    <t>Level of Cash (buffer)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +406,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -183,7 +431,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -200,12 +448,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -214,6 +491,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -67355,4 +67654,4482 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF828FB-C980-43DE-A75D-5DC6A0D571A4}">
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+    <col min="5" max="11" width="14.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="6">
+        <v>300000</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>1+E2</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:K2" si="0">1+F2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="6">
+        <v>375</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6">
+        <v>260</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="H5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="I5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="J5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="10">
+        <f>+G5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="H6" s="10">
+        <f>+H5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="I6" s="10">
+        <f>+I5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="J6" s="10">
+        <f>+J5*$B$5</f>
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6">
+        <v>110</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="1">
+        <f>+G5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="H7" s="1">
+        <f>+H5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="I7" s="1">
+        <f>+I5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="J7" s="1">
+        <f>+J5*$B$7</f>
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="11">
+        <f>+G6-G7</f>
+        <v>15000000</v>
+      </c>
+      <c r="H8" s="11">
+        <f>+H6-H7</f>
+        <v>15000000</v>
+      </c>
+      <c r="I8" s="11">
+        <f>+I6-I7</f>
+        <v>15000000</v>
+      </c>
+      <c r="J8" s="11">
+        <f>+J6-J7</f>
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6">
+        <f>+B9*B10*1</f>
+        <v>10000000</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <f>+B6</f>
+        <v>5000000</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6">
+        <v>7500000</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <f>+B11</f>
+        <v>10000000</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2800000</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="H13" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="I13" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="J13" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6">
+        <f>+B12/5</f>
+        <v>1500000</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="H14" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="I14" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="J14" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="K14" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="13">
+        <f>+SUM(F11:F14)</f>
+        <v>15000000</v>
+      </c>
+      <c r="G15" s="13">
+        <f t="shared" ref="G15:K15" si="1">+SUM(G11:G14)</f>
+        <v>4300000</v>
+      </c>
+      <c r="H15" s="13">
+        <f t="shared" si="1"/>
+        <v>4300000</v>
+      </c>
+      <c r="I15" s="13">
+        <f t="shared" si="1"/>
+        <v>4300000</v>
+      </c>
+      <c r="J15" s="13">
+        <f t="shared" si="1"/>
+        <v>4300000</v>
+      </c>
+      <c r="K15" s="13">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D17" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <f>+F8-F15</f>
+        <v>-15000000</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" ref="G17:K17" si="2">+G8-G15</f>
+        <v>10700000</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="2"/>
+        <v>10700000</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="2"/>
+        <v>10700000</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="2"/>
+        <v>10700000</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" si="2"/>
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="14">
+        <f>+F17*(1-$B$16)</f>
+        <v>-11850000</v>
+      </c>
+      <c r="G18" s="14">
+        <f t="shared" ref="G18:K18" si="3">+G17*(1-$B$16)</f>
+        <v>8453000</v>
+      </c>
+      <c r="H18" s="14">
+        <f t="shared" si="3"/>
+        <v>8453000</v>
+      </c>
+      <c r="I18" s="14">
+        <f t="shared" si="3"/>
+        <v>8453000</v>
+      </c>
+      <c r="J18" s="14">
+        <f t="shared" si="3"/>
+        <v>8453000</v>
+      </c>
+      <c r="K18" s="14">
+        <f t="shared" si="3"/>
+        <v>-1185000</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="1">
+        <f>+B12</f>
+        <v>7500000</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D22" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1">
+        <f>+F14</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <f>+G14</f>
+        <v>1500000</v>
+      </c>
+      <c r="H22" s="1">
+        <f>+H14</f>
+        <v>1500000</v>
+      </c>
+      <c r="I22" s="1">
+        <f>+I14</f>
+        <v>1500000</v>
+      </c>
+      <c r="J22" s="1">
+        <f>+J14</f>
+        <v>1500000</v>
+      </c>
+      <c r="K22" s="1">
+        <f>+K14</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="14">
+        <f>-E21+E22</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F23" s="14">
+        <f>-F21+F22</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <f>-G21+G22</f>
+        <v>1500000</v>
+      </c>
+      <c r="H23" s="14">
+        <f>-H21+H22</f>
+        <v>1500000</v>
+      </c>
+      <c r="I23" s="14">
+        <f>-I21+I22</f>
+        <v>1500000</v>
+      </c>
+      <c r="J23" s="14">
+        <f>-J21+J22</f>
+        <v>1500000</v>
+      </c>
+      <c r="K23" s="14">
+        <f>-K21+K22</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="28" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="16">
+        <f>+E27</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="16">
+        <f t="shared" ref="F28:K28" si="4">+F27</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="15">
+        <f>+E18+E23+E28</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F30" s="15">
+        <f t="shared" ref="F30:K30" si="5">+F18+F23+F28</f>
+        <v>-11850000</v>
+      </c>
+      <c r="G30" s="15">
+        <f t="shared" si="5"/>
+        <v>9953000</v>
+      </c>
+      <c r="H30" s="15">
+        <f t="shared" si="5"/>
+        <v>9953000</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" si="5"/>
+        <v>9953000</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" si="5"/>
+        <v>9953000</v>
+      </c>
+      <c r="K30" s="15">
+        <f t="shared" si="5"/>
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="31" spans="4:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="15">
+        <f>+E30/((1+$B$15)^E2)</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F31" s="15">
+        <f>+F30/((1+$B$15)^F2)</f>
+        <v>-10580357.142857142</v>
+      </c>
+      <c r="G31" s="15">
+        <f>+G30/((1+$B$15)^G2)</f>
+        <v>7934470.6632653046</v>
+      </c>
+      <c r="H31" s="15">
+        <f>+H30/((1+$B$15)^H2)</f>
+        <v>7084348.8064868785</v>
+      </c>
+      <c r="I31" s="15">
+        <f>+I30/((1+$B$15)^I2)</f>
+        <v>6325311.4343632851</v>
+      </c>
+      <c r="J31" s="15">
+        <f>+J30/((1+$B$15)^J2)</f>
+        <v>5647599.4949672185</v>
+      </c>
+      <c r="K31" s="15">
+        <f>+K30/((1+$B$15)^K2)</f>
+        <v>159588.803170856</v>
+      </c>
+    </row>
+    <row r="32" spans="4:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="17">
+        <f>+SUM(E31:K31)</f>
+        <v>9070962.059396401</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E33" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45006DC9-CE06-45E1-9E98-2B1061A9B956}">
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="11" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="6">
+        <v>300000</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>1+E2</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:K2" si="0">1+F2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="6">
+        <v>375</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6">
+        <v>260</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="H5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="I5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="J5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="10">
+        <f>+G5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" ref="H6:J6" si="1">+H5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6">
+        <v>110</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="1">
+        <f>+G5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="H7" s="1">
+        <f>+H5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="I7" s="1">
+        <f>+I5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="J7" s="1">
+        <f>+J5*$B$18</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="1">
+        <f>+G7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="H8" s="1">
+        <f>+H7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="I8" s="1">
+        <f>+I7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="J8" s="1">
+        <f>+J7*$B$19</f>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="13">
+        <f>+G6-G8</f>
+        <v>23500000</v>
+      </c>
+      <c r="H9" s="13">
+        <f>+H6-H8</f>
+        <v>23500000</v>
+      </c>
+      <c r="I9" s="13">
+        <f>+I6-I8</f>
+        <v>23500000</v>
+      </c>
+      <c r="J9" s="13">
+        <f>+J6-J8</f>
+        <v>23500000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6">
+        <f>+B9*B10*1</f>
+        <v>10000000</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="1">
+        <f>+G5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="H11" s="1">
+        <f>+H5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="I11" s="1">
+        <f>+I5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="J11" s="1">
+        <f>+J5*$B$7</f>
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6">
+        <v>7500000</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="1">
+        <f>+G7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="H12" s="1">
+        <f>+H7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="I12" s="1">
+        <f>+I7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="J12" s="1">
+        <f>+J7*$B$20</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2800000</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="19">
+        <f>+G11-G12</f>
+        <v>9500000</v>
+      </c>
+      <c r="H13" s="19">
+        <f t="shared" ref="H13:J13" si="2">+H11-H12</f>
+        <v>9500000</v>
+      </c>
+      <c r="I13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+      <c r="J13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6">
+        <f>+B12/5</f>
+        <v>1500000</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="11">
+        <f>+G9-G13</f>
+        <v>14000000</v>
+      </c>
+      <c r="H14" s="11">
+        <f t="shared" ref="H14:J14" si="3">+H9-H13</f>
+        <v>14000000</v>
+      </c>
+      <c r="I14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+      <c r="J14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <f>+B6</f>
+        <v>5000000</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <f>+B11</f>
+        <v>10000000</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="6">
+        <v>100</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="H19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="I19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="J19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="6">
+        <v>60</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="H20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="I20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="J20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="K20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="13">
+        <f>+SUM(F17:F20)</f>
+        <v>15000000</v>
+      </c>
+      <c r="G21" s="13">
+        <f t="shared" ref="G21:K21" si="4">+SUM(G17:G20)</f>
+        <v>4300000</v>
+      </c>
+      <c r="H21" s="13">
+        <f t="shared" si="4"/>
+        <v>4300000</v>
+      </c>
+      <c r="I21" s="13">
+        <f t="shared" si="4"/>
+        <v>4300000</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="4"/>
+        <v>4300000</v>
+      </c>
+      <c r="K21" s="13">
+        <f t="shared" si="4"/>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1">
+        <f>+F14-F21</f>
+        <v>-15000000</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" ref="G23:J23" si="5">+G14-G21</f>
+        <v>9700000</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="5"/>
+        <v>9700000</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="5"/>
+        <v>9700000</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="5"/>
+        <v>9700000</v>
+      </c>
+      <c r="K23" s="1">
+        <f>+K12-K21</f>
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="14">
+        <f>+F23*(1-$B$16)</f>
+        <v>-11850000</v>
+      </c>
+      <c r="G24" s="14">
+        <f t="shared" ref="G24:K24" si="6">+G23*(1-$B$16)</f>
+        <v>7663000</v>
+      </c>
+      <c r="H24" s="14">
+        <f t="shared" si="6"/>
+        <v>7663000</v>
+      </c>
+      <c r="I24" s="14">
+        <f t="shared" si="6"/>
+        <v>7663000</v>
+      </c>
+      <c r="J24" s="14">
+        <f t="shared" si="6"/>
+        <v>7663000</v>
+      </c>
+      <c r="K24" s="14">
+        <f t="shared" si="6"/>
+        <v>-1185000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="1">
+        <f>+B12</f>
+        <v>7500000</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1">
+        <f>+F20</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <f>+G20</f>
+        <v>1500000</v>
+      </c>
+      <c r="H28" s="1">
+        <f>+H20</f>
+        <v>1500000</v>
+      </c>
+      <c r="I28" s="1">
+        <f>+I20</f>
+        <v>1500000</v>
+      </c>
+      <c r="J28" s="1">
+        <f>+J20</f>
+        <v>1500000</v>
+      </c>
+      <c r="K28" s="1">
+        <f>+K20</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="14">
+        <f>-E27+E28</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F29" s="14">
+        <f>-F27+F28</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <f>-G27+G28</f>
+        <v>1500000</v>
+      </c>
+      <c r="H29" s="14">
+        <f>-H27+H28</f>
+        <v>1500000</v>
+      </c>
+      <c r="I29" s="14">
+        <f>-I27+I28</f>
+        <v>1500000</v>
+      </c>
+      <c r="J29" s="14">
+        <f>-J27+J28</f>
+        <v>1500000</v>
+      </c>
+      <c r="K29" s="14">
+        <f>-K27+K28</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="16">
+        <f>+E33</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="16">
+        <f t="shared" ref="F34:K34" si="7">+F33</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E36" s="15">
+        <f>+E24+E29+E34</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F36" s="15">
+        <f t="shared" ref="F36:K36" si="8">+F24+F29+F34</f>
+        <v>-11850000</v>
+      </c>
+      <c r="G36" s="15">
+        <f t="shared" si="8"/>
+        <v>9163000</v>
+      </c>
+      <c r="H36" s="15">
+        <f t="shared" si="8"/>
+        <v>9163000</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" si="8"/>
+        <v>9163000</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" si="8"/>
+        <v>9163000</v>
+      </c>
+      <c r="K36" s="15">
+        <f>+K24+K29+K34</f>
+        <v>315000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D37" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="15">
+        <f>+E36/((1+$B$15)^E2)</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F37" s="15">
+        <f>+F36/((1+$B$15)^F2)</f>
+        <v>-10580357.142857142</v>
+      </c>
+      <c r="G37" s="15">
+        <f>+G36/((1+$B$15)^G2)</f>
+        <v>7304687.4999999991</v>
+      </c>
+      <c r="H37" s="15">
+        <f>+H36/((1+$B$15)^H2)</f>
+        <v>6522042.4107142836</v>
+      </c>
+      <c r="I37" s="15">
+        <f>+I36/((1+$B$15)^I2)</f>
+        <v>5823252.1524234684</v>
+      </c>
+      <c r="J37" s="15">
+        <f>+J36/((1+$B$15)^J2)</f>
+        <v>5199332.2789495243</v>
+      </c>
+      <c r="K37" s="15">
+        <f>+K36/((1+$B$15)^K2)</f>
+        <v>159588.803170856</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="17">
+        <f>+SUM(E37:K37)</f>
+        <v>6928546.0024009906</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E39" s="18"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00C769D1-7ED6-4E23-B564-02EC0B5A8132}">
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="11" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="6">
+        <v>300000</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>1+E2</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:K2" si="0">1+F2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="6">
+        <v>375</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6">
+        <v>260</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="H5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="I5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="J5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="10">
+        <f>+G5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" ref="H6:J6" si="1">+H5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6">
+        <v>110</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="1">
+        <f>+G5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="H7" s="1">
+        <f>+H5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="I7" s="1">
+        <f>+I5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="J7" s="1">
+        <f>+J5*$B$18</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="1">
+        <f>+G7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="H8" s="1">
+        <f>+H7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="I8" s="1">
+        <f>+I7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="J8" s="1">
+        <f>+J7*$B$19</f>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="13">
+        <f>+G6-G8</f>
+        <v>23500000</v>
+      </c>
+      <c r="H9" s="13">
+        <f>+H6-H8</f>
+        <v>23500000</v>
+      </c>
+      <c r="I9" s="13">
+        <f>+I6-I8</f>
+        <v>23500000</v>
+      </c>
+      <c r="J9" s="13">
+        <f>+J6-J8</f>
+        <v>23500000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6">
+        <f>+B9*B10*1</f>
+        <v>10000000</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="1">
+        <f>+G5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="H11" s="1">
+        <f>+H5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="I11" s="1">
+        <f>+I5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="J11" s="1">
+        <f>+J5*$B$7</f>
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6">
+        <v>7500000</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="1">
+        <f>+G7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="H12" s="1">
+        <f>+H7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="I12" s="1">
+        <f>+I7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="J12" s="1">
+        <f>+J7*$B$20</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2800000</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="19">
+        <f>+G11-G12</f>
+        <v>9500000</v>
+      </c>
+      <c r="H13" s="19">
+        <f t="shared" ref="H13:J13" si="2">+H11-H12</f>
+        <v>9500000</v>
+      </c>
+      <c r="I13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+      <c r="J13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6">
+        <f>+B12/5</f>
+        <v>1500000</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="11">
+        <f>+G9-G13</f>
+        <v>14000000</v>
+      </c>
+      <c r="H14" s="11">
+        <f t="shared" ref="H14:J14" si="3">+H9-H13</f>
+        <v>14000000</v>
+      </c>
+      <c r="I14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+      <c r="J14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <f>+B6</f>
+        <v>5000000</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <f>+B11</f>
+        <v>10000000</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="6">
+        <v>100</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="H19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="I19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="J19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="6">
+        <v>60</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="H20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="I20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="J20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="K20" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="13">
+        <f>+SUM(F17:F20)</f>
+        <v>15000000</v>
+      </c>
+      <c r="G21" s="13">
+        <f t="shared" ref="G21:K21" si="4">+SUM(G17:G20)</f>
+        <v>4300000</v>
+      </c>
+      <c r="H21" s="13">
+        <f t="shared" si="4"/>
+        <v>4300000</v>
+      </c>
+      <c r="I21" s="13">
+        <f t="shared" si="4"/>
+        <v>4300000</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="4"/>
+        <v>4300000</v>
+      </c>
+      <c r="K21" s="13">
+        <f t="shared" si="4"/>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1">
+        <f>+F14-F21</f>
+        <v>-15000000</v>
+      </c>
+      <c r="G23" s="1">
+        <f t="shared" ref="G23:J23" si="5">+G14-G21</f>
+        <v>9700000</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="5"/>
+        <v>9700000</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="5"/>
+        <v>9700000</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="5"/>
+        <v>9700000</v>
+      </c>
+      <c r="K23" s="1">
+        <f>+K12-K21</f>
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D24" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="14">
+        <f>+F23*(1-$B$16)</f>
+        <v>-11850000</v>
+      </c>
+      <c r="G24" s="14">
+        <f t="shared" ref="G24:K24" si="6">+G23*(1-$B$16)</f>
+        <v>7663000</v>
+      </c>
+      <c r="H24" s="14">
+        <f t="shared" si="6"/>
+        <v>7663000</v>
+      </c>
+      <c r="I24" s="14">
+        <f t="shared" si="6"/>
+        <v>7663000</v>
+      </c>
+      <c r="J24" s="14">
+        <f t="shared" si="6"/>
+        <v>7663000</v>
+      </c>
+      <c r="K24" s="14">
+        <f t="shared" si="6"/>
+        <v>-1185000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="1">
+        <f>+B12</f>
+        <v>7500000</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1">
+        <f>+F20</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <f>+G20</f>
+        <v>1500000</v>
+      </c>
+      <c r="H28" s="1">
+        <f>+H20</f>
+        <v>1500000</v>
+      </c>
+      <c r="I28" s="1">
+        <f>+I20</f>
+        <v>1500000</v>
+      </c>
+      <c r="J28" s="1">
+        <f>+J20</f>
+        <v>1500000</v>
+      </c>
+      <c r="K28" s="1">
+        <f>+K20</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="14">
+        <f>-E27+E28</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F29" s="14">
+        <f>-F27+F28</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <f>-G27+G28</f>
+        <v>1500000</v>
+      </c>
+      <c r="H29" s="14">
+        <f>-H27+H28</f>
+        <v>1500000</v>
+      </c>
+      <c r="I29" s="14">
+        <f>-I27+I28</f>
+        <v>1500000</v>
+      </c>
+      <c r="J29" s="14">
+        <f>-J27+J28</f>
+        <v>1500000</v>
+      </c>
+      <c r="K29" s="14">
+        <f>-K27+K28</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1">
+        <f>+F9*$B$22</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <f>+G9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="H32" s="1">
+        <f>+H9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="I32" s="1">
+        <f>+I9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="J32" s="1">
+        <f>+J9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="K32" s="1">
+        <f>+K9*$B$22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1">
+        <f>+F13*$B$23</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <f>+G13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="H33" s="1">
+        <f>+H13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="I33" s="1">
+        <f>+I13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="J33" s="1">
+        <f>+J13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="K33" s="1">
+        <f>+K13*$B$23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="13">
+        <f>+F32-F33</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="13">
+        <f>+G32-G33</f>
+        <v>2100000</v>
+      </c>
+      <c r="H34" s="13">
+        <f>+H32-H33</f>
+        <v>2100000</v>
+      </c>
+      <c r="I34" s="13">
+        <f>+I32-I33</f>
+        <v>2100000</v>
+      </c>
+      <c r="J34" s="13">
+        <f>+J32-J33</f>
+        <v>2100000</v>
+      </c>
+      <c r="K34" s="13">
+        <f>+K32-K33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="1">
+        <f>+F34-E34</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <f>+G34-F34</f>
+        <v>2100000</v>
+      </c>
+      <c r="H35" s="1">
+        <f>+H34-G34</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <f>+I34-H34</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <f>+J34-I34</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <f>+K34-J34</f>
+        <v>-2100000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="16">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <f>-F35</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <f>-G35</f>
+        <v>-2100000</v>
+      </c>
+      <c r="H36" s="14">
+        <f>-H35</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="14">
+        <f>-I35</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="14">
+        <f>-J35</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="14">
+        <f>-K35</f>
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="15">
+        <f>+E24+E29+E36</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F38" s="15">
+        <f>+F24+F29+F36</f>
+        <v>-11850000</v>
+      </c>
+      <c r="G38" s="15">
+        <f>+G24+G29+G36</f>
+        <v>7063000</v>
+      </c>
+      <c r="H38" s="15">
+        <f>+H24+H29+H36</f>
+        <v>9163000</v>
+      </c>
+      <c r="I38" s="15">
+        <f>+I24+I29+I36</f>
+        <v>9163000</v>
+      </c>
+      <c r="J38" s="15">
+        <f>+J24+J29+J36</f>
+        <v>9163000</v>
+      </c>
+      <c r="K38" s="15">
+        <f>+K24+K29+K36</f>
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="15">
+        <f>+E38/((1+$B$15)^E2)</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F39" s="15">
+        <f>+F38/((1+$B$15)^F2)</f>
+        <v>-10580357.142857142</v>
+      </c>
+      <c r="G39" s="15">
+        <f>+G38/((1+$B$15)^G2)</f>
+        <v>5630580.3571428563</v>
+      </c>
+      <c r="H39" s="15">
+        <f>+H38/((1+$B$15)^H2)</f>
+        <v>6522042.4107142836</v>
+      </c>
+      <c r="I39" s="15">
+        <f>+I38/((1+$B$15)^I2)</f>
+        <v>5823252.1524234684</v>
+      </c>
+      <c r="J39" s="15">
+        <f>+J38/((1+$B$15)^J2)</f>
+        <v>5199332.2789495243</v>
+      </c>
+      <c r="K39" s="15">
+        <f>+K38/((1+$B$15)^K2)</f>
+        <v>1223514.1576432295</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="17">
+        <f>+SUM(E39:K39)</f>
+        <v>6318364.2140162205</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E41" s="18"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D39BF10-BAD8-4001-A45C-4284E27364D1}">
+  <dimension ref="A1:K43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="11" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="6">
+        <v>300000</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>1+E2</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:K2" si="0">1+F2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="6">
+        <v>375</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6">
+        <v>260</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="H5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="I5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="J5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="10">
+        <f>+G5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" ref="H6:J6" si="1">+H5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6">
+        <v>110</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="1">
+        <f>+G5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="H7" s="1">
+        <f>+H5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="I7" s="1">
+        <f>+I5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="J7" s="1">
+        <f>+J5*$B$18</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="1">
+        <f>+G7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="H8" s="1">
+        <f>+H7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="I8" s="1">
+        <f>+I7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="J8" s="1">
+        <f>+J7*$B$19</f>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="13">
+        <f>+G6-G8</f>
+        <v>23500000</v>
+      </c>
+      <c r="H9" s="13">
+        <f>+H6-H8</f>
+        <v>23500000</v>
+      </c>
+      <c r="I9" s="13">
+        <f>+I6-I8</f>
+        <v>23500000</v>
+      </c>
+      <c r="J9" s="13">
+        <f>+J6-J8</f>
+        <v>23500000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6">
+        <f>+B9*B10*1</f>
+        <v>10000000</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="1">
+        <f>+G5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="H11" s="1">
+        <f>+H5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="I11" s="1">
+        <f>+I5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="J11" s="1">
+        <f>+J5*$B$7</f>
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6">
+        <v>7500000</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="1">
+        <f>+G7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="H12" s="1">
+        <f>+H7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="I12" s="1">
+        <f>+I7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="J12" s="1">
+        <f>+J7*$B$20</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2800000</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="19">
+        <f>+G11-G12</f>
+        <v>9500000</v>
+      </c>
+      <c r="H13" s="19">
+        <f t="shared" ref="H13:J13" si="2">+H11-H12</f>
+        <v>9500000</v>
+      </c>
+      <c r="I13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+      <c r="J13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6">
+        <f>+B12/5</f>
+        <v>1500000</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="11">
+        <f>+G9-G13</f>
+        <v>14000000</v>
+      </c>
+      <c r="H14" s="11">
+        <f t="shared" ref="H14:J14" si="3">+H9-H13</f>
+        <v>14000000</v>
+      </c>
+      <c r="I14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+      <c r="J14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <f>+B6</f>
+        <v>5000000</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <f>+B11</f>
+        <v>10000000</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="6">
+        <v>100</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="H19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="I19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="J19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="6">
+        <v>60</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="G20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="H20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="I20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="J20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="H21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="I21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="J21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="K21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="13">
+        <f>+SUM(F17:F21)</f>
+        <v>15200000</v>
+      </c>
+      <c r="G22" s="13">
+        <f>+SUM(G17:G21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="H22" s="13">
+        <f>+SUM(H17:H21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="I22" s="13">
+        <f>+SUM(I17:I21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="J22" s="13">
+        <f>+SUM(J17:J21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="K22" s="13">
+        <f>+SUM(K17:K21)</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
+        <f>+F14-F22</f>
+        <v>-15200000</v>
+      </c>
+      <c r="G24" s="1">
+        <f>+G14-G22</f>
+        <v>9500000</v>
+      </c>
+      <c r="H24" s="1">
+        <f>+H14-H22</f>
+        <v>9500000</v>
+      </c>
+      <c r="I24" s="1">
+        <f>+I14-I22</f>
+        <v>9500000</v>
+      </c>
+      <c r="J24" s="1">
+        <f>+J14-J22</f>
+        <v>9500000</v>
+      </c>
+      <c r="K24" s="1">
+        <f>+K12-K22</f>
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="14">
+        <f>+F24*(1-$B$16)</f>
+        <v>-12008000</v>
+      </c>
+      <c r="G25" s="14">
+        <f t="shared" ref="G25:K25" si="4">+G24*(1-$B$16)</f>
+        <v>7505000</v>
+      </c>
+      <c r="H25" s="14">
+        <f t="shared" si="4"/>
+        <v>7505000</v>
+      </c>
+      <c r="I25" s="14">
+        <f t="shared" si="4"/>
+        <v>7505000</v>
+      </c>
+      <c r="J25" s="14">
+        <f t="shared" si="4"/>
+        <v>7505000</v>
+      </c>
+      <c r="K25" s="14">
+        <f t="shared" si="4"/>
+        <v>-1185000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="1">
+        <f>+B12</f>
+        <v>7500000</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1">
+        <f>+F21</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <f>+G21</f>
+        <v>1500000</v>
+      </c>
+      <c r="H29" s="1">
+        <f>+H21</f>
+        <v>1500000</v>
+      </c>
+      <c r="I29" s="1">
+        <f>+I21</f>
+        <v>1500000</v>
+      </c>
+      <c r="J29" s="1">
+        <f>+J21</f>
+        <v>1500000</v>
+      </c>
+      <c r="K29" s="1">
+        <f>+K21</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="14">
+        <f>-E28+E29</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F30" s="14">
+        <f>-F28+F29</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <f>-G28+G29</f>
+        <v>1500000</v>
+      </c>
+      <c r="H30" s="14">
+        <f>-H28+H29</f>
+        <v>1500000</v>
+      </c>
+      <c r="I30" s="14">
+        <f>-I28+I29</f>
+        <v>1500000</v>
+      </c>
+      <c r="J30" s="14">
+        <f>-J28+J29</f>
+        <v>1500000</v>
+      </c>
+      <c r="K30" s="14">
+        <f>-K28+K29</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1">
+        <f>+F9*$B$22</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <f>+G9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="H33" s="1">
+        <f>+H9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="I33" s="1">
+        <f>+I9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="J33" s="1">
+        <f>+J9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="K33" s="1">
+        <f>+K9*$B$22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1">
+        <f>+F13*$B$23</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <f>+G13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="H34" s="1">
+        <f>+H13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="I34" s="1">
+        <f>+I13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="J34" s="1">
+        <f>+J13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="K34" s="1">
+        <f>+K13*$B$23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="13">
+        <f>+F33-F34</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="13">
+        <f>+G33-G34</f>
+        <v>2100000</v>
+      </c>
+      <c r="H35" s="13">
+        <f>+H33-H34</f>
+        <v>2100000</v>
+      </c>
+      <c r="I35" s="13">
+        <f>+I33-I34</f>
+        <v>2100000</v>
+      </c>
+      <c r="J35" s="13">
+        <f>+J33-J34</f>
+        <v>2100000</v>
+      </c>
+      <c r="K35" s="13">
+        <f>+K33-K34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="1">
+        <f>+F35-E35</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <f>+G35-F35</f>
+        <v>2100000</v>
+      </c>
+      <c r="H36" s="1">
+        <f>+H35-G35</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <f>+I35-H35</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <f>+J35-I35</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <f>+K35-J35</f>
+        <v>-2100000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D37" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="16">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <f>-F36</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <f>-G36</f>
+        <v>-2100000</v>
+      </c>
+      <c r="H37" s="14">
+        <f>-H36</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="14">
+        <f>-I36</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="14">
+        <f>-J36</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="14">
+        <f>-K36</f>
+        <v>2100000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="15">
+        <f>+E25+E30+E37</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F39" s="15">
+        <f>+F25+F30+F37</f>
+        <v>-12008000</v>
+      </c>
+      <c r="G39" s="15">
+        <f>+G25+G30+G37</f>
+        <v>6905000</v>
+      </c>
+      <c r="H39" s="15">
+        <f>+H25+H30+H37</f>
+        <v>9005000</v>
+      </c>
+      <c r="I39" s="15">
+        <f>+I25+I30+I37</f>
+        <v>9005000</v>
+      </c>
+      <c r="J39" s="15">
+        <f>+J25+J30+J37</f>
+        <v>9005000</v>
+      </c>
+      <c r="K39" s="15">
+        <f>+K25+K30+K37</f>
+        <v>2415000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="15">
+        <f>+E39/((1+$B$15)^E2)</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F40" s="15">
+        <f>+F39/((1+$B$15)^F2)</f>
+        <v>-10721428.571428571</v>
+      </c>
+      <c r="G40" s="15">
+        <f>+G39/((1+$B$15)^G2)</f>
+        <v>5504623.724489795</v>
+      </c>
+      <c r="H40" s="15">
+        <f>+H39/((1+$B$15)^H2)</f>
+        <v>6409581.131559765</v>
+      </c>
+      <c r="I40" s="15">
+        <f>+I39/((1+$B$15)^I2)</f>
+        <v>5722840.2960355049</v>
+      </c>
+      <c r="J40" s="15">
+        <f>+J39/((1+$B$15)^J2)</f>
+        <v>5109678.8357459856</v>
+      </c>
+      <c r="K40" s="15">
+        <f>+K39/((1+$B$15)^K2)</f>
+        <v>1223514.1576432295</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D41" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="17">
+        <f>+SUM(E40:K40)</f>
+        <v>5748809.5740457093</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E42" s="18"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD1E543-8A61-4A95-BA99-ADF56796EF07}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="0.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="11" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="6">
+        <v>300000</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <f>1+E2</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:K2" si="0">1+F2</f>
+        <v>2</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J2" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="6">
+        <v>375</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="6">
+        <v>260</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="H5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="I5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+      <c r="J5" s="1">
+        <f>+$B$3</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="10">
+        <f>+G5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" ref="H6:J6" si="1">+H5*$B$5</f>
+        <v>26000000</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="1"/>
+        <v>26000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6">
+        <v>110</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="1">
+        <f>+G5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="H7" s="1">
+        <f>+H5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="I7" s="1">
+        <f>+I5*$B$18</f>
+        <v>25000</v>
+      </c>
+      <c r="J7" s="1">
+        <f>+J5*$B$18</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="1">
+        <f>+G7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="H8" s="1">
+        <f>+H7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="I8" s="1">
+        <f>+I7*$B$19</f>
+        <v>2500000</v>
+      </c>
+      <c r="J8" s="1">
+        <f>+J7*$B$19</f>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="13">
+        <f>+G6-G8</f>
+        <v>23500000</v>
+      </c>
+      <c r="H9" s="13">
+        <f>+H6-H8</f>
+        <v>23500000</v>
+      </c>
+      <c r="I9" s="13">
+        <f>+I6-I8</f>
+        <v>23500000</v>
+      </c>
+      <c r="J9" s="13">
+        <f>+J6-J8</f>
+        <v>23500000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="6">
+        <f>+B9*B10*1</f>
+        <v>10000000</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="1">
+        <f>+G5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="H11" s="1">
+        <f>+H5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="I11" s="1">
+        <f>+I5*$B$7</f>
+        <v>11000000</v>
+      </c>
+      <c r="J11" s="1">
+        <f>+J5*$B$7</f>
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="6">
+        <v>7500000</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="1">
+        <f>+G7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="H12" s="1">
+        <f>+H7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="I12" s="1">
+        <f>+I7*$B$20</f>
+        <v>1500000</v>
+      </c>
+      <c r="J12" s="1">
+        <f>+J7*$B$20</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6">
+        <v>2800000</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="19">
+        <f>+G11-G12</f>
+        <v>9500000</v>
+      </c>
+      <c r="H13" s="19">
+        <f t="shared" ref="H13:J13" si="2">+H11-H12</f>
+        <v>9500000</v>
+      </c>
+      <c r="I13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+      <c r="J13" s="19">
+        <f t="shared" si="2"/>
+        <v>9500000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="6">
+        <f>+B12/5</f>
+        <v>1500000</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="11">
+        <f>+G9-G13</f>
+        <v>14000000</v>
+      </c>
+      <c r="H14" s="11">
+        <f t="shared" ref="H14:J14" si="3">+H9-H13</f>
+        <v>14000000</v>
+      </c>
+      <c r="I14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+      <c r="J14" s="11">
+        <f t="shared" si="3"/>
+        <v>14000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <f>+B6</f>
+        <v>5000000</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <f>+B11</f>
+        <v>10000000</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="6">
+        <v>100</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="H19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="I19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+      <c r="J19" s="1">
+        <f>+$B$13</f>
+        <v>2800000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="6">
+        <v>60</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="G20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="H20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="I20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+      <c r="J20" s="1">
+        <f>+$B$24</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="H21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="I21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="J21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+      <c r="K21" s="1">
+        <f>+$B$14</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="13">
+        <f>+SUM(F17:F21)</f>
+        <v>15200000</v>
+      </c>
+      <c r="G22" s="13">
+        <f>+SUM(G17:G21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="H22" s="13">
+        <f>+SUM(H17:H21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="I22" s="13">
+        <f>+SUM(I17:I21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="J22" s="13">
+        <f>+SUM(J17:J21)</f>
+        <v>4500000</v>
+      </c>
+      <c r="K22" s="13">
+        <f>+SUM(K17:K21)</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="6">
+        <v>200000</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1">
+        <f>+F14-F22</f>
+        <v>-15200000</v>
+      </c>
+      <c r="G24" s="1">
+        <f>+G14-G22</f>
+        <v>9500000</v>
+      </c>
+      <c r="H24" s="1">
+        <f>+H14-H22</f>
+        <v>9500000</v>
+      </c>
+      <c r="I24" s="1">
+        <f>+I14-I22</f>
+        <v>9500000</v>
+      </c>
+      <c r="J24" s="1">
+        <f>+J14-J22</f>
+        <v>9500000</v>
+      </c>
+      <c r="K24" s="1">
+        <f>+K12-K22</f>
+        <v>-1500000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="6">
+        <v>1500000</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="14">
+        <f>+F24*(1-$B$16)</f>
+        <v>-12008000</v>
+      </c>
+      <c r="G25" s="14">
+        <f t="shared" ref="G25:K25" si="4">+G24*(1-$B$16)</f>
+        <v>7505000</v>
+      </c>
+      <c r="H25" s="14">
+        <f t="shared" si="4"/>
+        <v>7505000</v>
+      </c>
+      <c r="I25" s="14">
+        <f t="shared" si="4"/>
+        <v>7505000</v>
+      </c>
+      <c r="J25" s="14">
+        <f t="shared" si="4"/>
+        <v>7505000</v>
+      </c>
+      <c r="K25" s="14">
+        <f t="shared" si="4"/>
+        <v>-1185000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="1">
+        <f>+B12</f>
+        <v>7500000</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="9"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="9"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="9"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="9"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="9"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D34" s="9"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D35" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1">
+        <f>+F21</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <f>+G21</f>
+        <v>1500000</v>
+      </c>
+      <c r="H35" s="1">
+        <f>+H21</f>
+        <v>1500000</v>
+      </c>
+      <c r="I35" s="1">
+        <f>+I21</f>
+        <v>1500000</v>
+      </c>
+      <c r="J35" s="1">
+        <f>+J21</f>
+        <v>1500000</v>
+      </c>
+      <c r="K35" s="1">
+        <f>+K21</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D36" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" s="14">
+        <f>-E28+E35</f>
+        <v>-7500000</v>
+      </c>
+      <c r="F36" s="14">
+        <f>-F28+F35</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <f>-G28+G35</f>
+        <v>1500000</v>
+      </c>
+      <c r="H36" s="14">
+        <f>-H28+H35</f>
+        <v>1500000</v>
+      </c>
+      <c r="I36" s="14">
+        <f>-I28+I35</f>
+        <v>1500000</v>
+      </c>
+      <c r="J36" s="14">
+        <f>-J28+J35</f>
+        <v>1500000</v>
+      </c>
+      <c r="K36" s="14">
+        <f>-K28+K35</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D38" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D39" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="1">
+        <f>+B25</f>
+        <v>1500000</v>
+      </c>
+      <c r="F39" s="1">
+        <f>+E39</f>
+        <v>1500000</v>
+      </c>
+      <c r="G39" s="1">
+        <f>+F39</f>
+        <v>1500000</v>
+      </c>
+      <c r="H39" s="1">
+        <f>+G39</f>
+        <v>1500000</v>
+      </c>
+      <c r="I39" s="1">
+        <f>+H39</f>
+        <v>1500000</v>
+      </c>
+      <c r="J39" s="1">
+        <f>+I39</f>
+        <v>1500000</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D40" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1">
+        <f>+F9*$B$22</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <f>+G9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="H40" s="1">
+        <f>+H9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="I40" s="1">
+        <f>+I9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="J40" s="1">
+        <f>+J9*$B$22</f>
+        <v>3525000</v>
+      </c>
+      <c r="K40" s="1">
+        <f>+K9*$B$22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D41" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="1">
+        <f>+E13*$B$23</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <f>+F13*$B$23</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <f>+G13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="H41" s="1">
+        <f>+H13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="I41" s="1">
+        <f>+I13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="J41" s="1">
+        <f>+J13*$B$23</f>
+        <v>1425000</v>
+      </c>
+      <c r="K41" s="1">
+        <f>+K13*$B$23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D42" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="13">
+        <f>E39+E40-E41</f>
+        <v>1500000</v>
+      </c>
+      <c r="F42" s="13">
+        <f t="shared" ref="F42:K42" si="5">F39+F40-F41</f>
+        <v>1500000</v>
+      </c>
+      <c r="G42" s="13">
+        <f t="shared" si="5"/>
+        <v>3600000</v>
+      </c>
+      <c r="H42" s="13">
+        <f t="shared" si="5"/>
+        <v>3600000</v>
+      </c>
+      <c r="I42" s="13">
+        <f t="shared" si="5"/>
+        <v>3600000</v>
+      </c>
+      <c r="J42" s="13">
+        <f t="shared" si="5"/>
+        <v>3600000</v>
+      </c>
+      <c r="K42" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D43" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E43" s="1">
+        <f>+E42-0</f>
+        <v>1500000</v>
+      </c>
+      <c r="F43" s="1">
+        <f>+F42-E42</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <f>+G42-F42</f>
+        <v>2100000</v>
+      </c>
+      <c r="H43" s="1">
+        <f>+H42-G42</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <f>+I42-H42</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <f>+J42-I42</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <f>+K42-J42</f>
+        <v>-3600000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D44" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E44" s="14">
+        <f>-E43</f>
+        <v>-1500000</v>
+      </c>
+      <c r="F44" s="14">
+        <f>-F43</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <f>-G43</f>
+        <v>-2100000</v>
+      </c>
+      <c r="H44" s="14">
+        <f>-H43</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="14">
+        <f>-I43</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="14">
+        <f>-J43</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="14">
+        <f>-K43</f>
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="15">
+        <f>+E25+E36+E44</f>
+        <v>-9000000</v>
+      </c>
+      <c r="F46" s="15">
+        <f>+F25+F36+F44</f>
+        <v>-12008000</v>
+      </c>
+      <c r="G46" s="15">
+        <f>+G25+G36+G44</f>
+        <v>6905000</v>
+      </c>
+      <c r="H46" s="15">
+        <f>+H25+H36+H44</f>
+        <v>9005000</v>
+      </c>
+      <c r="I46" s="15">
+        <f>+I25+I36+I44</f>
+        <v>9005000</v>
+      </c>
+      <c r="J46" s="15">
+        <f>+J25+J36+J44</f>
+        <v>9005000</v>
+      </c>
+      <c r="K46" s="15">
+        <f>+K25+K36+K44</f>
+        <v>3915000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D47" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="15">
+        <f>+E46/((1+$B$15)^E2)</f>
+        <v>-9000000</v>
+      </c>
+      <c r="F47" s="15">
+        <f>+F46/((1+$B$15)^F2)</f>
+        <v>-10721428.571428571</v>
+      </c>
+      <c r="G47" s="15">
+        <f>+G46/((1+$B$15)^G2)</f>
+        <v>5504623.724489795</v>
+      </c>
+      <c r="H47" s="15">
+        <f>+H46/((1+$B$15)^H2)</f>
+        <v>6409581.131559765</v>
+      </c>
+      <c r="I47" s="15">
+        <f>+I46/((1+$B$15)^I2)</f>
+        <v>5722840.2960355049</v>
+      </c>
+      <c r="J47" s="15">
+        <f>+J46/((1+$B$15)^J2)</f>
+        <v>5109678.8357459856</v>
+      </c>
+      <c r="K47" s="15">
+        <f>+K46/((1+$B$15)^K2)</f>
+        <v>1983460.8394092105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="17">
+        <f>+SUM(E47:K47)</f>
+        <v>5008756.2558116904</v>
+      </c>
+    </row>
+    <row r="49" spans="4:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="E49" s="18"/>
+    </row>
+    <row r="50" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>